--- a/src/analyses/linear_regression/SubmissionTo.xlsx
+++ b/src/analyses/linear_regression/SubmissionTo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,16 +477,16 @@
         <v>45195</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,11 +496,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.5153169247190711</v>
+        <v>0.3929687362084489</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +511,16 @@
         <v>45195</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.2750768803736463</v>
+        <v>0.5250839845213338</v>
       </c>
     </row>
     <row r="4">
@@ -545,16 +545,16 @@
         <v>45195</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -564,11 +564,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.5430847104441212</v>
+        <v>0.3777188218451177</v>
       </c>
     </row>
     <row r="5">
@@ -579,16 +579,16 @@
         <v>45195</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -598,11 +598,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5503311145234199</v>
+        <v>0.4569476759924023</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +613,16 @@
         <v>45195</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(100.0, 200.0)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -632,11 +632,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.779727809607017</v>
+        <v>0.78125</v>
       </c>
     </row>
     <row r="7">
@@ -647,16 +647,16 @@
         <v>45195</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_007_Unit 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(100.0, 200.0)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -666,11 +666,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4188602709120804</v>
+        <v>0.4642228269569393</v>
       </c>
     </row>
     <row r="8">
@@ -681,16 +681,16 @@
         <v>45195</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_027_Unit 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(150.0, 350.0)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -700,11 +700,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5706388689563047</v>
+        <v>0.4579824253000693</v>
       </c>
     </row>
     <row r="9">
@@ -715,16 +715,16 @@
         <v>45195</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -734,11 +734,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5214491214652535</v>
+        <v>0.3832694415674847</v>
       </c>
     </row>
     <row r="10">
@@ -749,16 +749,16 @@
         <v>45195</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,11 +768,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.2520727354178601</v>
+        <v>0.4055035228775322</v>
       </c>
     </row>
     <row r="11">
@@ -783,16 +783,16 @@
         <v>45195</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -802,11 +802,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3917962302315166</v>
+        <v>0.3713586114597018</v>
       </c>
     </row>
     <row r="12">
@@ -814,19 +814,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -836,11 +836,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.4218993668364904</v>
+        <v>0.3350026467442317</v>
       </c>
     </row>
     <row r="13">
@@ -848,19 +848,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -870,11 +870,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.5158799389063158</v>
+        <v>0.3138527146001467</v>
       </c>
     </row>
     <row r="14">
@@ -882,19 +882,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.7679538396092742</v>
+        <v>0.6276516233384652</v>
       </c>
     </row>
     <row r="15">
@@ -916,19 +916,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -938,11 +938,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.5011950560648013</v>
+        <v>0.4418180364243434</v>
       </c>
     </row>
     <row r="16">
@@ -950,19 +950,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -972,11 +972,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.644255118931818</v>
+        <v>0.479566578718745</v>
       </c>
     </row>
     <row r="17">
@@ -984,19 +984,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.6547901770575475</v>
+        <v>0.4354590429779143</v>
       </c>
     </row>
     <row r="18">
@@ -1018,19 +1018,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1040,11 +1040,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.3770946490926249</v>
+        <v>0.3745962647206439</v>
       </c>
     </row>
     <row r="19">
@@ -1052,19 +1052,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1074,11 +1074,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.3929687362084489</v>
+        <v>0.4383550623845213</v>
       </c>
     </row>
     <row r="20">
@@ -1086,19 +1086,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1108,11 +1108,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.5250839845213338</v>
+        <v>0.7113406188549125</v>
       </c>
     </row>
     <row r="21">
@@ -1120,19 +1120,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3777188218451177</v>
+        <v>0.6608634682821721</v>
       </c>
     </row>
     <row r="22">
@@ -1154,19 +1154,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.4569476759924023</v>
+        <v>0.6262967830187306</v>
       </c>
     </row>
     <row r="23">
@@ -1191,16 +1191,16 @@
         <v>45202</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(200.0, 400.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.309564603012678</v>
+        <v>0.5179890285801343</v>
       </c>
     </row>
     <row r="24">
@@ -1225,16 +1225,16 @@
         <v>45202</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_026_Unit 1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(1900.0, 2000.0)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1244,11 +1244,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.3410602472179867</v>
+        <v>0.3841605462011124</v>
       </c>
     </row>
     <row r="25">
@@ -1259,16 +1259,16 @@
         <v>45202</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.4297340848424414</v>
+        <v>0.705059289949282</v>
       </c>
     </row>
     <row r="26">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1312,11 +1312,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.2639270383136363</v>
+        <v>0.4003260396527001</v>
       </c>
     </row>
     <row r="27">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.6462992364472782</v>
+        <v>0.4297638030990436</v>
       </c>
     </row>
     <row r="28">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.5048770508493856</v>
+        <v>0.2716915446335556</v>
       </c>
     </row>
     <row r="29">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.5558468127033944</v>
+        <v>0.3291490814685047</v>
       </c>
     </row>
     <row r="30">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.4221475642847913</v>
+        <v>0.4100217387333077</v>
       </c>
     </row>
     <row r="31">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.2774059777439513</v>
+        <v>0.3158177219586158</v>
       </c>
     </row>
     <row r="32">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.2797395670534013</v>
+        <v>0.4488158383729181</v>
       </c>
     </row>
     <row r="33">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.4488158383729181</v>
+        <v>0.4147796015488553</v>
       </c>
     </row>
     <row r="34">
@@ -1584,11 +1584,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.4147796015488553</v>
+        <v>0.2724311035650184</v>
       </c>
     </row>
     <row r="35">
@@ -1618,11 +1618,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.2724311035650184</v>
+        <v>0.3300644051734213</v>
       </c>
     </row>
     <row r="36">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.3300644051734213</v>
+        <v>0.3450407661387828</v>
       </c>
     </row>
     <row r="37">
@@ -1664,19 +1664,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.3450407661387828</v>
+        <v>0.2820243121816352</v>
       </c>
     </row>
     <row r="38">
@@ -1698,19 +1698,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(100.0, 700.0)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1720,11 +1720,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.3232323232323233</v>
+        <v>0.2772956653637478</v>
       </c>
     </row>
     <row r="39">
@@ -1732,19 +1732,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1754,11 +1754,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.4066519972918078</v>
+        <v>0.2772727272727274</v>
       </c>
     </row>
     <row r="40">
@@ -1766,19 +1766,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.7407586578057822</v>
+        <v>0.2826639878598755</v>
       </c>
     </row>
     <row r="41">
@@ -1800,19 +1800,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_020_Unit 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1822,11 +1822,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.4175423018104683</v>
+        <v>0.2514891031862966</v>
       </c>
     </row>
     <row r="42">
@@ -1834,19 +1834,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1856,11 +1856,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8287197441438064</v>
+        <v>0.3408161647499637</v>
       </c>
     </row>
     <row r="43">
@@ -1868,19 +1868,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.8274093651788054</v>
+        <v>0.2732463053756177</v>
       </c>
     </row>
     <row r="44">
@@ -1902,19 +1902,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1924,11 +1924,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.8103084478651634</v>
+        <v>0.2751679774773331</v>
       </c>
     </row>
     <row r="45">
@@ -1936,19 +1936,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.4603968010506435</v>
+        <v>0.2513861232745549</v>
       </c>
     </row>
     <row r="46">
@@ -1970,19 +1970,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
+          <t>(100.0, 450.0)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1992,11 +1992,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.3359437309130469</v>
+        <v>0.3185361991226358</v>
       </c>
     </row>
     <row r="47">
@@ -2004,19 +2004,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.3978649029451905</v>
+        <v>0.2730866082168256</v>
       </c>
     </row>
     <row r="48">
@@ -2038,19 +2038,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45209</v>
+        <v>45203</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2060,11 +2060,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.3240174320196226</v>
+        <v>0.397487315508301</v>
       </c>
     </row>
     <row r="49">
@@ -2072,19 +2072,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(1050.0, 1150.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.4748824406468632</v>
+        <v>0.3425750400526518</v>
       </c>
     </row>
     <row r="50">
@@ -2106,19 +2106,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(1950.0, 2050.0)</t>
+          <t>(0.0, 700.0)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2128,11 +2128,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.50648423605255</v>
+        <v>0.3346914111785183</v>
       </c>
     </row>
     <row r="51">
@@ -2140,19 +2140,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(0.0, 700.0)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.3122396052827648</v>
+        <v>0.2863493348573712</v>
       </c>
     </row>
     <row r="52">
@@ -2174,19 +2174,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_021_Unit 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 450.0)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.2711424018356952</v>
+        <v>0.3210127571417078</v>
       </c>
     </row>
     <row r="53">
@@ -2208,19 +2208,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 650.0)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2230,11 +2230,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.3697120266582056</v>
+        <v>0.4928768477513044</v>
       </c>
     </row>
     <row r="54">
@@ -2242,19 +2242,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 650.0)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2264,11 +2264,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.3739011837550115</v>
+        <v>0.4183397319752765</v>
       </c>
     </row>
     <row r="55">
@@ -2276,19 +2276,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(1600.0, 1700.0)</t>
+          <t>(350.0, 650.0)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5523496410094144</v>
+        <v>0.5153219837157662</v>
       </c>
     </row>
     <row r="56">
@@ -2310,19 +2310,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(350.0, 650.0)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2332,11 +2332,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4674327619233987</v>
+        <v>0.2625307536025649</v>
       </c>
     </row>
     <row r="57">
@@ -2344,19 +2344,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C57" t="n">
         <v>4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(0.0, 750.0)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2366,11 +2366,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.3218535846427673</v>
+        <v>0.4824680074699437</v>
       </c>
     </row>
     <row r="58">
@@ -2378,19 +2378,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C58" t="n">
         <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(0.0, 750.0)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.5971579701169192</v>
+        <v>0.4266777760013774</v>
       </c>
     </row>
     <row r="59">
@@ -2412,19 +2412,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C59" t="n">
         <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(250.0, 750.0)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2434,11 +2434,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.3543381911649756</v>
+        <v>0.5160518310093134</v>
       </c>
     </row>
     <row r="60">
@@ -2446,19 +2446,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(250.0, 750.0)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.3511179097802641</v>
+        <v>0.2774396938423414</v>
       </c>
     </row>
     <row r="61">
@@ -2480,19 +2480,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45226</v>
+        <v>45204</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2502,11 +2502,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.4106961767395518</v>
+        <v>0.2858599592114208</v>
       </c>
     </row>
     <row r="62">
@@ -2514,19 +2514,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45226</v>
+        <v>45204</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.2651848225767361</v>
+        <v>0.3089958836477688</v>
       </c>
     </row>
     <row r="63">
@@ -2548,19 +2548,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45226</v>
+        <v>45204</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_004</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.5715870525418407</v>
+        <v>0.2794102149874191</v>
       </c>
     </row>
     <row r="64">
@@ -2582,19 +2582,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45226</v>
+        <v>45204</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(500.0, 850.0)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2604,11 +2604,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.3402866217987159</v>
+        <v>0.2576688606611129</v>
       </c>
     </row>
     <row r="65">
@@ -2616,19 +2616,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45226</v>
+        <v>45204</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(50.0, 350.0)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.5244822077762548</v>
+        <v>0.3116077957587511</v>
       </c>
     </row>
     <row r="66">
@@ -2650,19 +2650,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45252</v>
+        <v>45204</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(1900.0, 2050.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.3313938872435948</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="67">
@@ -2684,19 +2684,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45271</v>
+        <v>45204</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Channel.C_030</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(400.0, 500.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2869256586927867</v>
+        <v>0.4926108374384237</v>
       </c>
     </row>
     <row r="68">
@@ -2718,19 +2718,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45274</v>
+        <v>45204</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2740,11 +2740,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.2912399797790135</v>
+        <v>0.3441280476456356</v>
       </c>
     </row>
     <row r="69">
@@ -2752,19 +2752,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45274</v>
+        <v>45204</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_019_Unit 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(2200.0, 2300.0)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2774,11 +2774,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.5169042584972219</v>
+        <v>0.3758104180639392</v>
       </c>
     </row>
     <row r="70">
@@ -2786,19 +2786,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45274</v>
+        <v>45209</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_007</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(1150.0, 1250.0)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.4029442346561021</v>
+        <v>0.3775606428442447</v>
       </c>
     </row>
     <row r="71">
@@ -2820,19 +2820,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45274</v>
+        <v>45209</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_007</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(1150.0, 1250.0)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2842,11 +2842,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.4211671383738615</v>
+        <v>0.3477758638159894</v>
       </c>
     </row>
     <row r="72">
@@ -2854,19 +2854,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45274</v>
+        <v>45209</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2724406138322472</v>
+        <v>0.6941616689732946</v>
       </c>
     </row>
     <row r="73">
@@ -2888,19 +2888,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45278</v>
+        <v>45209</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2910,11 +2910,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.4847473088852399</v>
+        <v>0.9140086488430603</v>
       </c>
     </row>
     <row r="74">
@@ -2922,19 +2922,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45278</v>
+        <v>45209</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2944,11 +2944,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.5016132341147728</v>
+        <v>0.3506924377662194</v>
       </c>
     </row>
     <row r="75">
@@ -2956,19 +2956,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45278</v>
+        <v>45209</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.3306782859600789</v>
+        <v>0.6733706734659654</v>
       </c>
     </row>
     <row r="76">
@@ -2990,19 +2990,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45195</v>
+        <v>45209</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3012,11 +3012,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.3832694415674847</v>
+        <v>0.8336166432837419</v>
       </c>
     </row>
     <row r="77">
@@ -3024,19 +3024,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45195</v>
+        <v>45209</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3046,11 +3046,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.4055035228775322</v>
+        <v>0.6754537045244313</v>
       </c>
     </row>
     <row r="78">
@@ -3058,19 +3058,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45195</v>
+        <v>45209</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.3713586114597018</v>
+        <v>0.4027872880331897</v>
       </c>
     </row>
     <row r="79">
@@ -3092,19 +3092,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45202</v>
+        <v>45209</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3114,11 +3114,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.705059289949282</v>
+        <v>0.5872590500442008</v>
       </c>
     </row>
     <row r="80">
@@ -3126,19 +3126,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.2772956653637478</v>
+        <v>0.3363272975426181</v>
       </c>
     </row>
     <row r="81">
@@ -3160,19 +3160,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Channel.C_018_Unit 1</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3182,11 +3182,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.2826639878598755</v>
+        <v>0.3293892940908686</v>
       </c>
     </row>
     <row r="82">
@@ -3194,19 +3194,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Channel.C_020_Unit 2</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.2514891031862966</v>
+        <v>0.4302962125098637</v>
       </c>
     </row>
     <row r="83">
@@ -3228,19 +3228,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.2730866082168256</v>
+        <v>0.2957652686011432</v>
       </c>
     </row>
     <row r="84">
@@ -3262,19 +3262,19 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.397487315508301</v>
+        <v>0.4816027740319784</v>
       </c>
     </row>
     <row r="85">
@@ -3296,19 +3296,19 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.3425750400526518</v>
+        <v>0.6457673550853051</v>
       </c>
     </row>
     <row r="86">
@@ -3330,19 +3330,19 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 3</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3352,11 +3352,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.3346914111785183</v>
+        <v>0.5610080004254893</v>
       </c>
     </row>
     <row r="87">
@@ -3364,19 +3364,19 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 3</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3386,11 +3386,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.2863493348573712</v>
+        <v>0.6571685241851717</v>
       </c>
     </row>
     <row r="88">
@@ -3398,19 +3398,19 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Channel.C_022_Unit 2</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3420,11 +3420,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.4824680074699437</v>
+        <v>0.578509559653932</v>
       </c>
     </row>
     <row r="89">
@@ -3432,19 +3432,19 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Channel.C_022_Unit 2</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3454,11 +3454,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.4266777760013774</v>
+        <v>0.9767316017316018</v>
       </c>
     </row>
     <row r="90">
@@ -3466,19 +3466,19 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.5160518310093134</v>
+        <v>0.7466559388514532</v>
       </c>
     </row>
     <row r="91">
@@ -3500,19 +3500,19 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45203</v>
+        <v>45210</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3522,11 +3522,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.2774396938423414</v>
+        <v>0.2713632597099667</v>
       </c>
     </row>
     <row r="92">
@@ -3534,19 +3534,19 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45204</v>
+        <v>45210</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Channel.C_004</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.3089958836477688</v>
+        <v>0.4680046888938584</v>
       </c>
     </row>
     <row r="93">
@@ -3568,19 +3568,19 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45204</v>
+        <v>45210</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Channel.C_004</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3590,11 +3590,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.2794102149874191</v>
+        <v>0.282410470700676</v>
       </c>
     </row>
     <row r="94">
@@ -3772,10 +3772,10 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3794,11 +3794,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.4330210772833725</v>
+        <v>0.3122396052827648</v>
       </c>
     </row>
     <row r="100">
@@ -3806,10 +3806,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.2937882070214679</v>
+        <v>0.2711424018356952</v>
       </c>
     </row>
     <row r="101">
@@ -3840,10 +3840,10 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45223</v>
+        <v>45210</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.2569186841927825</v>
+        <v>0.3697120266582056</v>
       </c>
     </row>
     <row r="102">
@@ -3874,19 +3874,19 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45238</v>
+        <v>45210</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Channel.C_007</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3896,11 +3896,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.2798536142263214</v>
+        <v>0.3739011837550115</v>
       </c>
     </row>
     <row r="103">
@@ -3908,10 +3908,10 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45238</v>
+        <v>45226</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1750.0, 1900.0)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3930,11 +3930,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.4343549753697828</v>
+        <v>0.6944444444444444</v>
       </c>
     </row>
     <row r="104">
@@ -3942,10 +3942,10 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45238</v>
+        <v>45226</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1750.0, 1900.0)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3964,11 +3964,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.3525181984621019</v>
+        <v>0.6620084251948641</v>
       </c>
     </row>
     <row r="105">
@@ -3976,10 +3976,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45238</v>
+        <v>45226</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1750.0, 1900.0)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.4617930223550593</v>
+        <v>0.6296170059542014</v>
       </c>
     </row>
     <row r="106">
@@ -4010,32 +4010,1698 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(1750.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.4906732559194701</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>(1750.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.7733041903283355</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(1750.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.6223085640278452</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.6868864309107576</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.2503050503754153</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(1600.0, 1900.0)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.4682003742393476</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.4851809637271682</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.3382762563388898</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.6260012402758967</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.2938013215531058</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.2891108641236252</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4351081088354566</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4106961767395518</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.2651848225767361</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5715870525418407</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3402866217987159</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5244822077762548</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>(850.0, 950.0)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0.9002976190476191</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>(850.0, 950.0)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0.4426229508196722</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Channel.C_019</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3119954519613416</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>(350.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0.3635626326389921</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>(350.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0.4594372077979357</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>(650.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0.6886940079546194</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>(650.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0.2664005209660523</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>(900.0, 1050.0)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2578912444303627</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Channel.C_024</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3111484321908965</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0.7126084441873916</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3319672131147542</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0.8019025367156208</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0.6970759773013872</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0.5074949304846854</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4304561972155039</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5782407385276676</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4895420197162262</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3917962302315166</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0.4218993668364904</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0.5158799389063158</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0.7679538396092742</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0.5011950560648013</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0.644255118931818</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0.6547901770575475</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>0.3770946490926249</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0.4330210772833725</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>0.2937882070214679</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0.2569186841927825</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
         <v>45238</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C151" t="n">
         <v>1</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>(100.0, 700.0)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>SubmissionTo</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>0.2798536142263214</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>0.4343549753697828</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0.3525181984621019</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>0.4617930223550593</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SubmissionTo</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>151J</t>
         </is>
       </c>
-      <c r="H106" t="n">
+      <c r="H155" t="n">
         <v>0.2894743106526481</v>
       </c>
     </row>
